--- a/ERP_Project_Timeplan_2026-2027.xlsx
+++ b/ERP_Project_Timeplan_2026-2027.xlsx
@@ -2174,7 +2174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J162"/>
+  <dimension ref="A1:J163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="63" min="1" max="1"/>
@@ -4484,6 +4484,49 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>54</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>6</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Purchasing / Masterdata</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Master data repair  (1) UOM enum expanded: added Ctn, Box, Cone, Pack, Liter, Set, Sheet, Lusin, Ball; (2) _detect_material_category rewritten with full Indonesian keywords (isolasi, lem, jarum, plastik, karton, kapas, benang, dacron); (3) bom_explosion + get_bom_materials UOM fix (.value extraction); (4) POST /masterdata/categories/seed-defaults endpoint; (5) SQL migrations 008 (UOM ALTER TYPE) + 009 (seed categories); (6) AdminMasterdataPage UOM_OPTIONS updated + Seed button added; (7) PO ACCESSORIES refer-from-PO-KAIN completed</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>products.py, purchasing.py, masterdata.py, AdminMasterdataPage.tsx, sql_migrations/008_uom_expansion.sql, sql_migrations/009_seed_material_categories.sql</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>done Done</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Run 008+009 SQL migrations on prod; Test BOM explosion per PO type; Test seed categories button</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -4499,7 +4542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:K138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="63" min="1" max="1"/>
@@ -7702,6 +7745,171 @@
       <c r="K135" t="inlineStr">
         <is>
           <t>Batch material_map with Product.id.in_() before loop</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BUG-034</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> High</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Masterdata / UOM</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>UOM enum missing Ctn/Box/Cone/Pack/Liter/Set/Sheet/Lusin/Ball  importing products with these UOM values caused DB errors</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Enum defined only 7 values (Pcs/Meter/Yard/Kg/Roll/Cm/Gram), no Indonesian manufacturing units</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Fixed</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>54</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Added 9 values to UOM enum in products.py + ALTER TYPE migration 008</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>BUG-035</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> High</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>BOM / Purchasing</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>_detect_material_category did not recognize Indonesian keywords: isolasi, lem, jarum, plastik, karton, kapas, benang  all fell to ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Function only checked English keywords; DB category names were generic (RAW/FG/WIP). Indonesian product names undetected.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Fixed</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>54</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Full rewrite with Indonesian keyword fallback + DB category prefix matching; SQL migration 009 seeds proper categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>BUG-036</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Med</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>BOM / UOM Display</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>BOM explosion showed UOM as Python enum object (e.g. &lt;UOM.METER: Meter&gt;) instead of string value</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>getattr(component, .uom., .PCS.) returns enum object; missing .value extraction</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Fixed</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>54</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Fixed in both get_bom_materials and bom_explosion to use component.uom.value</t>
         </is>
       </c>
     </row>
